--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.31262053353829</v>
+        <v>7.363300836699973</v>
       </c>
       <c r="D2" t="n">
-        <v>45.53571254798569</v>
+        <v>7.399553289047675</v>
       </c>
       <c r="E2" t="n">
-        <v>11.53414241988113</v>
+        <v>1.874298143230684</v>
       </c>
       <c r="F2" t="n">
-        <v>11.34562209357211</v>
+        <v>1.843663590205468</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.81539340296689</v>
+        <v>6.63250142798212</v>
       </c>
       <c r="D3" t="n">
-        <v>41.01365701862064</v>
+        <v>6.664719265525854</v>
       </c>
       <c r="E3" t="n">
-        <v>11.53414241988113</v>
+        <v>1.874298143230684</v>
       </c>
       <c r="F3" t="n">
-        <v>11.34562209357211</v>
+        <v>1.843663590205468</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>67.21965221385709</v>
+        <v>10.92319348475178</v>
       </c>
       <c r="D4" t="n">
-        <v>67.02162971202371</v>
+        <v>10.89101482820385</v>
       </c>
       <c r="E4" t="n">
-        <v>11.53414241988113</v>
+        <v>1.874298143230684</v>
       </c>
       <c r="F4" t="n">
-        <v>11.34562209357211</v>
+        <v>1.843663590205468</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
